--- a/docs/design/ACSMS-SCR-007/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_支店マスタ登録画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-007/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_支店マスタ登録画面_V1.0.xlsx
@@ -1701,7 +1701,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2127,7 +2127,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2695,7 +2695,7 @@
       <c r="U14" s="11" t="n"/>
       <c r="V14" s="19" t="inlineStr">
         <is>
-          <t>同一の支店コードが既に登録されています。</t>
+          <t>支店コード「{shiten_code}」はすでに登録されています。</t>
         </is>
       </c>
       <c r="W14" s="10" t="n"/>
@@ -2942,7 +2942,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3440,7 +3440,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -5212,7 +5212,7 @@
   "data": {
     "shiten_id": 1,
     "ja_id": 1,
-    "shiten_code": "S01",
+    "shiten_code": "001",
     "shiten_name": "本店営業部",
     "shiten_name_kana": "ホンテンエイギョウブ",
     "kinyu_shiten_flg": false,
@@ -5275,7 +5275,7 @@
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
-  "message": "セッションが切れました。再度ログインしてください"
+  "message": "セッションが切れました。再度ログインしてください。"
 }</t>
         </is>
       </c>
@@ -5326,7 +5326,7 @@
         <is>
           <t>{
   "error_code": "FORBIDDEN",
-  "message": "この画面へのアクセス権限がありません"
+  "message": "この画面へのアクセス権限がありません。"
 }</t>
         </is>
       </c>
@@ -5377,7 +5377,7 @@
         <is>
           <t>{
   "error_code": "NOT_FOUND",
-  "message": "指定された支店が見つかりません"
+  "message": "指定された支店が見つかりません。"
 }</t>
         </is>
       </c>
@@ -5428,7 +5428,7 @@
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
-  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください。"
 }</t>
         </is>
       </c>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="162" customHeight="1">
+    <row r="78" ht="144" customHeight="1">
       <c r="C78" s="42" t="inlineStr">
         <is>
           <t>SELECT shiten_id, ja_id, shiten_code, shiten_name, shiten_name_kana,
@@ -5583,7 +5583,6 @@
        kanri_shiten_id, biko, created_at, updated_at
 FROM m_shiten
 WHERE shiten_id = :shiten_id
-  AND ja_id = :ja_id
   AND deleted_at IS NULL</t>
         </is>
       </c>
@@ -5632,7 +5631,7 @@
     <row r="80" ht="18" customHeight="1">
       <c r="C80" s="41" t="inlineStr">
         <is>
-          <t>ja_id が一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
+          <t>レコードは存在するが `ja_id` がログインユーザーのスコープと一致しない場合も</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK113"/>
+  <dimension ref="A1:AK124"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -6025,7 +6024,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6772,7 +6771,7 @@
       <c r="W24" s="10" t="n"/>
       <c r="X24" s="11" t="n"/>
       <c r="Y24" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z24" s="10" t="n"/>
       <c r="AA24" s="10" t="n"/>
@@ -6784,7 +6783,7 @@
       <c r="AE24" s="11" t="n"/>
       <c r="AF24" s="19" t="inlineStr">
         <is>
-          <t>支店コード（半角数字3桁）</t>
+          <t>支店コード（半角数字3桁固定）</t>
         </is>
       </c>
       <c r="AG24" s="10" t="n"/>
@@ -6970,7 +6969,7 @@
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>管理支店ID（プルダウン選択値）</t>
+          <t>管理支店ID（プルダウン選択値、m_kanri_shitenに存在すること）</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -7039,7 +7038,7 @@
       <c r="AJ28" s="10" t="n"/>
       <c r="AK28" s="11" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1">
+    <row r="29" ht="36" customHeight="1">
       <c r="B29" s="31" t="n">
         <v>6</v>
       </c>
@@ -7074,7 +7073,7 @@
       <c r="S29" s="11" t="n"/>
       <c r="T29" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>△※</t>
         </is>
       </c>
       <c r="U29" s="10" t="n"/>
@@ -7092,7 +7091,7 @@
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>JASTEM_データ送信取扱店舗コード※空文字許容</t>
+          <t>JASTEM_データ送信取扱店舗コード。kinyu_shiten_flg=true 時は必須（必須項目です。）、false 時は空文字許容</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -7101,7 +7100,7 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1">
+    <row r="30" ht="36" customHeight="1">
       <c r="B30" s="31" t="n">
         <v>7</v>
       </c>
@@ -7136,7 +7135,7 @@
       <c r="S30" s="11" t="n"/>
       <c r="T30" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>△※</t>
         </is>
       </c>
       <c r="U30" s="10" t="n"/>
@@ -7154,7 +7153,7 @@
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>JASTEM_店舗名※空文字許容</t>
+          <t>JASTEM_店舗名。kinyu_shiten_flg=true 時は必須（必須項目です。）、false 時は空文字許容</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -7163,7 +7162,7 @@
       <c r="AJ30" s="10" t="n"/>
       <c r="AK30" s="11" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1">
+    <row r="31" ht="36" customHeight="1">
       <c r="B31" s="31" t="n">
         <v>8</v>
       </c>
@@ -7198,7 +7197,7 @@
       <c r="S31" s="11" t="n"/>
       <c r="T31" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>△※</t>
         </is>
       </c>
       <c r="U31" s="10" t="n"/>
@@ -7216,7 +7215,7 @@
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>JASTEM_貯金種別※空文字許容</t>
+          <t>JASTEM_貯金種別。kinyu_shiten_flg=true 時は必須（必須項目です。）、false 時は空文字許容</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -7225,7 +7224,7 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1">
+    <row r="32" ht="36" customHeight="1">
       <c r="B32" s="31" t="n">
         <v>9</v>
       </c>
@@ -7260,7 +7259,7 @@
       <c r="S32" s="11" t="n"/>
       <c r="T32" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>△※</t>
         </is>
       </c>
       <c r="U32" s="10" t="n"/>
@@ -7278,7 +7277,7 @@
       <c r="AE32" s="11" t="n"/>
       <c r="AF32" s="19" t="inlineStr">
         <is>
-          <t>JASTEM_口座番号※空文字許容</t>
+          <t>JASTEM_口座番号。kinyu_shiten_flg=true 時は必須（必須項目です。）、false 時は空文字許容</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -7333,7 +7332,9 @@
       <c r="Z33" s="10" t="n"/>
       <c r="AA33" s="10" t="n"/>
       <c r="AB33" s="11" t="n"/>
-      <c r="AC33" s="17" t="inlineStr"/>
+      <c r="AC33" s="17" t="n">
+        <v>500</v>
+      </c>
       <c r="AD33" s="10" t="n"/>
       <c r="AE33" s="11" t="n"/>
       <c r="AF33" s="19" t="inlineStr">
@@ -8344,7 +8345,7 @@
           <t>POST /api/v1/shiten
 Content-Type: application/json
 {
-  "shiten_code": "S01",
+  "shiten_code": "001",
   "shiten_name": "本店営業部",
   "shiten_name_kana": "ホンテンエイギョウブ",
   "kanri_shiten_id": 1,
@@ -8406,7 +8407,7 @@
   "data": {
     "shiten_id": 10,
     "ja_id": 1,
-    "shiten_code": "S01",
+    "shiten_code": "001",
     "shiten_name": "本店営業部",
     "shiten_name_kana": "ホンテンエイギョウブ",
     "kinyu_shiten_flg": false,
@@ -8417,7 +8418,7 @@
     "kanri_shiten_id": 1,
     "biko": "本店ビル1F",
     "created_at": "2026-04-14T10:00:00Z",
-    "updated_at": null
+    "updated_at": "2026-04-14T10:00:00Z"
   }
 }</t>
         </is>
@@ -8469,10 +8470,10 @@
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
-  "message": "入力値が不正です。詳細はerrorsフィールドを確認してください",
+  "message": "入力値が不正です。詳細はerrorsフィールドを確認してください。",
   "errors": [
-    { "field": "shiten_code", "message": "支店コードは必須です" },
-    { "field": "shiten_name", "message": "支店名は必須です" }
+    { "field": "shiten_code", "message": "支店コードを入力してください。" },
+    { "field": "shiten_name", "message": "支店名を入力してください。" }
   ]
 }</t>
         </is>
@@ -8524,7 +8525,7 @@
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
-  "message": "セッションが切れました。再度ログインしてください"
+  "message": "セッションが切れました。再度ログインしてください。"
 }</t>
         </is>
       </c>
@@ -8575,7 +8576,7 @@
         <is>
           <t>{
   "error_code": "FORBIDDEN",
-  "message": "この画面へのアクセス権限がありません"
+  "message": "この画面へのアクセス権限がありません。"
 }</t>
         </is>
       </c>
@@ -8626,7 +8627,7 @@
         <is>
           <t>{
   "error_code": "DUPLICATE_CODE",
-  "message": "同一の支店コードが既に登録されています"
+  "message": "支店コード「001」はすでに登録されています。"
 }</t>
         </is>
       </c>
@@ -8668,7 +8669,7 @@
     <row r="72" ht="19.5" customHeight="1">
       <c r="B72" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 500 Internal Server Error）</t>
+          <t>レスポンス（失敗 400 Bad Request（管理支店IDが存在しない場合））</t>
         </is>
       </c>
     </row>
@@ -8676,8 +8677,8 @@
       <c r="C73" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "INTERNAL_SERVER_ERROR",
-  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+  "error_code": "BAD_REQUEST",
+  "message": "管理支店IDが存在しません。"
 }</t>
         </is>
       </c>
@@ -8716,200 +8717,337 @@
       <c r="AJ73" s="10" t="n"/>
       <c r="AK73" s="11" t="n"/>
     </row>
-    <row r="75" ht="19.5" customHeight="1"/>
-    <row r="76" ht="19.5" customHeight="1">
-      <c r="A76" s="27" t="inlineStr">
+    <row r="75" ht="19.5" customHeight="1">
+      <c r="B75" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 403 Forbidden（管理支店IDが別JAに属する場合））</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="72" customHeight="1">
+      <c r="C76" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "DATA_SCOPE_VIOLATION",
+  "message": "このデータへのアクセス権限がありません。"
+}</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="10" t="n"/>
+      <c r="J76" s="10" t="n"/>
+      <c r="K76" s="10" t="n"/>
+      <c r="L76" s="10" t="n"/>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="10" t="n"/>
+      <c r="Q76" s="10" t="n"/>
+      <c r="R76" s="10" t="n"/>
+      <c r="S76" s="10" t="n"/>
+      <c r="T76" s="10" t="n"/>
+      <c r="U76" s="10" t="n"/>
+      <c r="V76" s="10" t="n"/>
+      <c r="W76" s="10" t="n"/>
+      <c r="X76" s="10" t="n"/>
+      <c r="Y76" s="10" t="n"/>
+      <c r="Z76" s="10" t="n"/>
+      <c r="AA76" s="10" t="n"/>
+      <c r="AB76" s="10" t="n"/>
+      <c r="AC76" s="10" t="n"/>
+      <c r="AD76" s="10" t="n"/>
+      <c r="AE76" s="10" t="n"/>
+      <c r="AF76" s="10" t="n"/>
+      <c r="AG76" s="10" t="n"/>
+      <c r="AH76" s="10" t="n"/>
+      <c r="AI76" s="10" t="n"/>
+      <c r="AJ76" s="10" t="n"/>
+      <c r="AK76" s="11" t="n"/>
+    </row>
+    <row r="78" ht="19.5" customHeight="1">
+      <c r="B78" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 500 Internal Server Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="72" customHeight="1">
+      <c r="C79" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "INTERNAL_SERVER_ERROR",
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください。"
+}</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="10" t="n"/>
+      <c r="J79" s="10" t="n"/>
+      <c r="K79" s="10" t="n"/>
+      <c r="L79" s="10" t="n"/>
+      <c r="M79" s="10" t="n"/>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="10" t="n"/>
+      <c r="Q79" s="10" t="n"/>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="10" t="n"/>
+      <c r="T79" s="10" t="n"/>
+      <c r="U79" s="10" t="n"/>
+      <c r="V79" s="10" t="n"/>
+      <c r="W79" s="10" t="n"/>
+      <c r="X79" s="10" t="n"/>
+      <c r="Y79" s="10" t="n"/>
+      <c r="Z79" s="10" t="n"/>
+      <c r="AA79" s="10" t="n"/>
+      <c r="AB79" s="10" t="n"/>
+      <c r="AC79" s="10" t="n"/>
+      <c r="AD79" s="10" t="n"/>
+      <c r="AE79" s="10" t="n"/>
+      <c r="AF79" s="10" t="n"/>
+      <c r="AG79" s="10" t="n"/>
+      <c r="AH79" s="10" t="n"/>
+      <c r="AI79" s="10" t="n"/>
+      <c r="AJ79" s="10" t="n"/>
+      <c r="AK79" s="11" t="n"/>
+    </row>
+    <row r="81" ht="19.5" customHeight="1"/>
+    <row r="82" ht="19.5" customHeight="1">
+      <c r="A82" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="54" customHeight="1">
-      <c r="B77" s="42" t="inlineStr">
+    <row r="83" ht="54" customHeight="1">
+      <c r="B83" s="42" t="inlineStr">
         <is>
           <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
 いずれかが失敗した場合は全てロールバックすること。
 例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
         </is>
       </c>
-      <c r="C77" s="10" t="n"/>
-      <c r="D77" s="10" t="n"/>
-      <c r="E77" s="10" t="n"/>
-      <c r="F77" s="10" t="n"/>
-      <c r="G77" s="10" t="n"/>
-      <c r="H77" s="10" t="n"/>
-      <c r="I77" s="10" t="n"/>
-      <c r="J77" s="10" t="n"/>
-      <c r="K77" s="10" t="n"/>
-      <c r="L77" s="10" t="n"/>
-      <c r="M77" s="10" t="n"/>
-      <c r="N77" s="10" t="n"/>
-      <c r="O77" s="10" t="n"/>
-      <c r="P77" s="10" t="n"/>
-      <c r="Q77" s="10" t="n"/>
-      <c r="R77" s="10" t="n"/>
-      <c r="S77" s="10" t="n"/>
-      <c r="T77" s="10" t="n"/>
-      <c r="U77" s="10" t="n"/>
-      <c r="V77" s="10" t="n"/>
-      <c r="W77" s="10" t="n"/>
-      <c r="X77" s="10" t="n"/>
-      <c r="Y77" s="10" t="n"/>
-      <c r="Z77" s="10" t="n"/>
-      <c r="AA77" s="10" t="n"/>
-      <c r="AB77" s="10" t="n"/>
-      <c r="AC77" s="10" t="n"/>
-      <c r="AD77" s="10" t="n"/>
-      <c r="AE77" s="10" t="n"/>
-      <c r="AF77" s="10" t="n"/>
-      <c r="AG77" s="10" t="n"/>
-      <c r="AH77" s="10" t="n"/>
-      <c r="AI77" s="10" t="n"/>
-      <c r="AJ77" s="10" t="n"/>
-      <c r="AK77" s="11" t="n"/>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="B78" s="27" t="inlineStr">
+      <c r="C83" s="10" t="n"/>
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
+      <c r="H83" s="10" t="n"/>
+      <c r="I83" s="10" t="n"/>
+      <c r="J83" s="10" t="n"/>
+      <c r="K83" s="10" t="n"/>
+      <c r="L83" s="10" t="n"/>
+      <c r="M83" s="10" t="n"/>
+      <c r="N83" s="10" t="n"/>
+      <c r="O83" s="10" t="n"/>
+      <c r="P83" s="10" t="n"/>
+      <c r="Q83" s="10" t="n"/>
+      <c r="R83" s="10" t="n"/>
+      <c r="S83" s="10" t="n"/>
+      <c r="T83" s="10" t="n"/>
+      <c r="U83" s="10" t="n"/>
+      <c r="V83" s="10" t="n"/>
+      <c r="W83" s="10" t="n"/>
+      <c r="X83" s="10" t="n"/>
+      <c r="Y83" s="10" t="n"/>
+      <c r="Z83" s="10" t="n"/>
+      <c r="AA83" s="10" t="n"/>
+      <c r="AB83" s="10" t="n"/>
+      <c r="AC83" s="10" t="n"/>
+      <c r="AD83" s="10" t="n"/>
+      <c r="AE83" s="10" t="n"/>
+      <c r="AF83" s="10" t="n"/>
+      <c r="AG83" s="10" t="n"/>
+      <c r="AH83" s="10" t="n"/>
+      <c r="AI83" s="10" t="n"/>
+      <c r="AJ83" s="10" t="n"/>
+      <c r="AK83" s="11" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="B84" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="C79" s="41" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="C85" s="41" t="inlineStr">
         <is>
           <t>リクエストボディの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="D80" s="41" t="inlineStr">
-        <is>
-          <t>shiten_code：必須、半角数字3桁固定</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="D81" s="41" t="inlineStr">
-        <is>
-          <t>shiten_name：必須、最大100桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="D82" s="41" t="inlineStr">
-        <is>
-          <t>shiten_name_kana：任意、最大100桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="D83" s="41" t="inlineStr">
-        <is>
-          <t>kanri_shiten_id：必須、数値型チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="D84" s="41" t="inlineStr">
-        <is>
-          <t>kinyu_shiten_flg：任意、ブール値（未指定の場合はデフォルト false）</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="D85" s="41" t="inlineStr">
-        <is>
-          <t>jastem_toriatsukai_tenpo_code：任意、最大3桁</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="D86" s="41" t="inlineStr">
         <is>
-          <t>jastem_tenpo_name：任意、最大15桁</t>
+          <t>shiten_code：必須、半角数字3桁固定</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="D87" s="41" t="inlineStr">
         <is>
-          <t>jastem_tyokin_shubetsu：任意、最大1桁</t>
+          <t>shiten_name：必須、最大100桁</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="D88" s="41" t="inlineStr">
         <is>
-          <t>jastem_koza_no：任意、最大7桁</t>
+          <t>shiten_name_kana：任意、最大100桁</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="D89" s="41" t="inlineStr">
         <is>
+          <t>kanri_shiten_id：必須、数値型チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="D90" s="41" t="inlineStr">
+        <is>
+          <t>kinyu_shiten_flg：任意、ブール値（未指定の場合はデフォルト false）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="D91" s="41" t="inlineStr">
+        <is>
+          <t>jastem_toriatsukai_tenpo_code：任意、最大3桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="D92" s="41" t="inlineStr">
+        <is>
+          <t>jastem_tenpo_name：任意、最大15桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="D93" s="41" t="inlineStr">
+        <is>
+          <t>jastem_tyokin_shubetsu：任意、最大1桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="D94" s="41" t="inlineStr">
+        <is>
+          <t>jastem_koza_no：任意、最大7桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="D95" s="41" t="inlineStr">
+        <is>
           <t>biko：任意、文字列</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="36" customHeight="1">
-      <c r="C90" s="41" t="inlineStr">
+    <row r="96" ht="36" customHeight="1">
+      <c r="C96" s="41" t="inlineStr">
         <is>
           <t>バリデーションエラーの場合：HTTP 400 (`VALIDATION_ERROR`) + errors配列</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="C91" s="41" t="inlineStr">
+    <row r="97" ht="18" customHeight="1">
+      <c r="B97" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="C98" s="41" t="inlineStr">
         <is>
           <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="C92" s="41" t="inlineStr">
+    <row r="99" ht="18" customHeight="1">
+      <c r="C99" s="41" t="inlineStr">
         <is>
           <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="36" customHeight="1">
-      <c r="D93" s="41" t="inlineStr">
+    <row r="100" ht="18" customHeight="1">
+      <c r="C100" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：`shiten.create` を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="36" customHeight="1">
+      <c r="D101" s="41" t="inlineStr">
         <is>
           <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="C94" s="41" t="inlineStr">
+    <row r="102" ht="18" customHeight="1">
+      <c r="C102" s="41" t="inlineStr">
         <is>
           <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="B95" s="27" t="inlineStr">
-        <is>
-          <t>4.3 重複チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="C96" s="41" t="inlineStr">
+    <row r="103" ht="18" customHeight="1">
+      <c r="B103" s="27" t="inlineStr">
+        <is>
+          <t>4.3 管理支店IDの検証・重複チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="C104" s="41" t="inlineStr">
         <is>
           <t>ログインユーザーのスコープを取得する（ja_id）。</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="C97" s="41" t="inlineStr">
-        <is>
-          <t>以下の条件で重複を確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="72" customHeight="1">
-      <c r="C98" s="42" t="inlineStr">
+    <row r="105" ht="36" customHeight="1">
+      <c r="C105" s="41" t="inlineStr">
+        <is>
+          <t>kanri_shiten_id が m_kanri_shiten に存在し、かつログインユーザーの ja_id に</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="36" customHeight="1">
+      <c r="D106" s="41" t="inlineStr">
+        <is>
+          <t>レコードが存在しない場合：HTTP 400 (`BAD_REQUEST`) `管理支店IDが存在しません。`</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="36" customHeight="1">
+      <c r="D107" s="41" t="inlineStr">
+        <is>
+          <t>レコードは存在するが ja_id が異なる場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="C108" s="41" t="inlineStr">
+        <is>
+          <t>以下の条件で shiten_code の重複を確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="72" customHeight="1">
+      <c r="C109" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) FROM m_shiten
 WHERE ja_id = :ja_id
@@ -8917,71 +9055,71 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D98" s="10" t="n"/>
-      <c r="E98" s="10" t="n"/>
-      <c r="F98" s="10" t="n"/>
-      <c r="G98" s="10" t="n"/>
-      <c r="H98" s="10" t="n"/>
-      <c r="I98" s="10" t="n"/>
-      <c r="J98" s="10" t="n"/>
-      <c r="K98" s="10" t="n"/>
-      <c r="L98" s="10" t="n"/>
-      <c r="M98" s="10" t="n"/>
-      <c r="N98" s="10" t="n"/>
-      <c r="O98" s="10" t="n"/>
-      <c r="P98" s="10" t="n"/>
-      <c r="Q98" s="10" t="n"/>
-      <c r="R98" s="10" t="n"/>
-      <c r="S98" s="10" t="n"/>
-      <c r="T98" s="10" t="n"/>
-      <c r="U98" s="10" t="n"/>
-      <c r="V98" s="10" t="n"/>
-      <c r="W98" s="10" t="n"/>
-      <c r="X98" s="10" t="n"/>
-      <c r="Y98" s="10" t="n"/>
-      <c r="Z98" s="10" t="n"/>
-      <c r="AA98" s="10" t="n"/>
-      <c r="AB98" s="10" t="n"/>
-      <c r="AC98" s="10" t="n"/>
-      <c r="AD98" s="10" t="n"/>
-      <c r="AE98" s="10" t="n"/>
-      <c r="AF98" s="10" t="n"/>
-      <c r="AG98" s="10" t="n"/>
-      <c r="AH98" s="10" t="n"/>
-      <c r="AI98" s="10" t="n"/>
-      <c r="AJ98" s="10" t="n"/>
-      <c r="AK98" s="11" t="n"/>
-    </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="C99" s="41" t="inlineStr">
+      <c r="D109" s="10" t="n"/>
+      <c r="E109" s="10" t="n"/>
+      <c r="F109" s="10" t="n"/>
+      <c r="G109" s="10" t="n"/>
+      <c r="H109" s="10" t="n"/>
+      <c r="I109" s="10" t="n"/>
+      <c r="J109" s="10" t="n"/>
+      <c r="K109" s="10" t="n"/>
+      <c r="L109" s="10" t="n"/>
+      <c r="M109" s="10" t="n"/>
+      <c r="N109" s="10" t="n"/>
+      <c r="O109" s="10" t="n"/>
+      <c r="P109" s="10" t="n"/>
+      <c r="Q109" s="10" t="n"/>
+      <c r="R109" s="10" t="n"/>
+      <c r="S109" s="10" t="n"/>
+      <c r="T109" s="10" t="n"/>
+      <c r="U109" s="10" t="n"/>
+      <c r="V109" s="10" t="n"/>
+      <c r="W109" s="10" t="n"/>
+      <c r="X109" s="10" t="n"/>
+      <c r="Y109" s="10" t="n"/>
+      <c r="Z109" s="10" t="n"/>
+      <c r="AA109" s="10" t="n"/>
+      <c r="AB109" s="10" t="n"/>
+      <c r="AC109" s="10" t="n"/>
+      <c r="AD109" s="10" t="n"/>
+      <c r="AE109" s="10" t="n"/>
+      <c r="AF109" s="10" t="n"/>
+      <c r="AG109" s="10" t="n"/>
+      <c r="AH109" s="10" t="n"/>
+      <c r="AI109" s="10" t="n"/>
+      <c r="AJ109" s="10" t="n"/>
+      <c r="AK109" s="11" t="n"/>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="C110" s="41" t="inlineStr">
         <is>
           <t>重複がある場合：HTTP 400 (`DUPLICATE_CODE`)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="B100" s="27" t="inlineStr">
+    <row r="111" ht="18" customHeight="1">
+      <c r="B111" s="27" t="inlineStr">
         <is>
           <t>4.4 データ登録</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="36" customHeight="1">
-      <c r="C101" s="41" t="inlineStr">
+    <row r="112" ht="36" customHeight="1">
+      <c r="C112" s="41" t="inlineStr">
         <is>
           <t>kinyu_shiten_flg はリクエストから取得する（未提供の場合はデフォルト値 false）。</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="C102" s="41" t="inlineStr">
+    <row r="113" ht="18" customHeight="1">
+      <c r="C113" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して登録する。</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="234" customHeight="1">
-      <c r="C103" s="42" t="inlineStr">
+    <row r="114" ht="234" customHeight="1">
+      <c r="C114" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO m_shiten (ja_id, shiten_code, shiten_name, shiten_name_kana,
                       kinyu_shiten_flg,
@@ -8998,57 +9136,57 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D103" s="10" t="n"/>
-      <c r="E103" s="10" t="n"/>
-      <c r="F103" s="10" t="n"/>
-      <c r="G103" s="10" t="n"/>
-      <c r="H103" s="10" t="n"/>
-      <c r="I103" s="10" t="n"/>
-      <c r="J103" s="10" t="n"/>
-      <c r="K103" s="10" t="n"/>
-      <c r="L103" s="10" t="n"/>
-      <c r="M103" s="10" t="n"/>
-      <c r="N103" s="10" t="n"/>
-      <c r="O103" s="10" t="n"/>
-      <c r="P103" s="10" t="n"/>
-      <c r="Q103" s="10" t="n"/>
-      <c r="R103" s="10" t="n"/>
-      <c r="S103" s="10" t="n"/>
-      <c r="T103" s="10" t="n"/>
-      <c r="U103" s="10" t="n"/>
-      <c r="V103" s="10" t="n"/>
-      <c r="W103" s="10" t="n"/>
-      <c r="X103" s="10" t="n"/>
-      <c r="Y103" s="10" t="n"/>
-      <c r="Z103" s="10" t="n"/>
-      <c r="AA103" s="10" t="n"/>
-      <c r="AB103" s="10" t="n"/>
-      <c r="AC103" s="10" t="n"/>
-      <c r="AD103" s="10" t="n"/>
-      <c r="AE103" s="10" t="n"/>
-      <c r="AF103" s="10" t="n"/>
-      <c r="AG103" s="10" t="n"/>
-      <c r="AH103" s="10" t="n"/>
-      <c r="AI103" s="10" t="n"/>
-      <c r="AJ103" s="10" t="n"/>
-      <c r="AK103" s="11" t="n"/>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="B104" s="27" t="inlineStr">
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="10" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
+      <c r="H114" s="10" t="n"/>
+      <c r="I114" s="10" t="n"/>
+      <c r="J114" s="10" t="n"/>
+      <c r="K114" s="10" t="n"/>
+      <c r="L114" s="10" t="n"/>
+      <c r="M114" s="10" t="n"/>
+      <c r="N114" s="10" t="n"/>
+      <c r="O114" s="10" t="n"/>
+      <c r="P114" s="10" t="n"/>
+      <c r="Q114" s="10" t="n"/>
+      <c r="R114" s="10" t="n"/>
+      <c r="S114" s="10" t="n"/>
+      <c r="T114" s="10" t="n"/>
+      <c r="U114" s="10" t="n"/>
+      <c r="V114" s="10" t="n"/>
+      <c r="W114" s="10" t="n"/>
+      <c r="X114" s="10" t="n"/>
+      <c r="Y114" s="10" t="n"/>
+      <c r="Z114" s="10" t="n"/>
+      <c r="AA114" s="10" t="n"/>
+      <c r="AB114" s="10" t="n"/>
+      <c r="AC114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="10" t="n"/>
+      <c r="AF114" s="10" t="n"/>
+      <c r="AG114" s="10" t="n"/>
+      <c r="AH114" s="10" t="n"/>
+      <c r="AI114" s="10" t="n"/>
+      <c r="AJ114" s="10" t="n"/>
+      <c r="AK114" s="11" t="n"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="B115" s="27" t="inlineStr">
         <is>
           <t>4.5 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="C105" s="41" t="inlineStr">
+    <row r="116" ht="18" customHeight="1">
+      <c r="C116" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="216" customHeight="1">
-      <c r="C106" s="42" t="inlineStr">
+    <row r="117" ht="216" customHeight="1">
+      <c r="C117" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -9064,50 +9202,50 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D106" s="10" t="n"/>
-      <c r="E106" s="10" t="n"/>
-      <c r="F106" s="10" t="n"/>
-      <c r="G106" s="10" t="n"/>
-      <c r="H106" s="10" t="n"/>
-      <c r="I106" s="10" t="n"/>
-      <c r="J106" s="10" t="n"/>
-      <c r="K106" s="10" t="n"/>
-      <c r="L106" s="10" t="n"/>
-      <c r="M106" s="10" t="n"/>
-      <c r="N106" s="10" t="n"/>
-      <c r="O106" s="10" t="n"/>
-      <c r="P106" s="10" t="n"/>
-      <c r="Q106" s="10" t="n"/>
-      <c r="R106" s="10" t="n"/>
-      <c r="S106" s="10" t="n"/>
-      <c r="T106" s="10" t="n"/>
-      <c r="U106" s="10" t="n"/>
-      <c r="V106" s="10" t="n"/>
-      <c r="W106" s="10" t="n"/>
-      <c r="X106" s="10" t="n"/>
-      <c r="Y106" s="10" t="n"/>
-      <c r="Z106" s="10" t="n"/>
-      <c r="AA106" s="10" t="n"/>
-      <c r="AB106" s="10" t="n"/>
-      <c r="AC106" s="10" t="n"/>
-      <c r="AD106" s="10" t="n"/>
-      <c r="AE106" s="10" t="n"/>
-      <c r="AF106" s="10" t="n"/>
-      <c r="AG106" s="10" t="n"/>
-      <c r="AH106" s="10" t="n"/>
-      <c r="AI106" s="10" t="n"/>
-      <c r="AJ106" s="10" t="n"/>
-      <c r="AK106" s="11" t="n"/>
-    </row>
-    <row r="107" ht="306" customHeight="1">
-      <c r="C107" s="42" t="inlineStr">
+      <c r="D117" s="10" t="n"/>
+      <c r="E117" s="10" t="n"/>
+      <c r="F117" s="10" t="n"/>
+      <c r="G117" s="10" t="n"/>
+      <c r="H117" s="10" t="n"/>
+      <c r="I117" s="10" t="n"/>
+      <c r="J117" s="10" t="n"/>
+      <c r="K117" s="10" t="n"/>
+      <c r="L117" s="10" t="n"/>
+      <c r="M117" s="10" t="n"/>
+      <c r="N117" s="10" t="n"/>
+      <c r="O117" s="10" t="n"/>
+      <c r="P117" s="10" t="n"/>
+      <c r="Q117" s="10" t="n"/>
+      <c r="R117" s="10" t="n"/>
+      <c r="S117" s="10" t="n"/>
+      <c r="T117" s="10" t="n"/>
+      <c r="U117" s="10" t="n"/>
+      <c r="V117" s="10" t="n"/>
+      <c r="W117" s="10" t="n"/>
+      <c r="X117" s="10" t="n"/>
+      <c r="Y117" s="10" t="n"/>
+      <c r="Z117" s="10" t="n"/>
+      <c r="AA117" s="10" t="n"/>
+      <c r="AB117" s="10" t="n"/>
+      <c r="AC117" s="10" t="n"/>
+      <c r="AD117" s="10" t="n"/>
+      <c r="AE117" s="10" t="n"/>
+      <c r="AF117" s="10" t="n"/>
+      <c r="AG117" s="10" t="n"/>
+      <c r="AH117" s="10" t="n"/>
+      <c r="AI117" s="10" t="n"/>
+      <c r="AJ117" s="10" t="n"/>
+      <c r="AK117" s="11" t="n"/>
+    </row>
+    <row r="118" ht="306" customHeight="1">
+      <c r="C118" s="42" t="inlineStr">
         <is>
           <t>`before_value`：INSERT のため空文字列を設定する。
 `after_value`：登録されたデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
 {
   "shiten_id": 10,
   "ja_id": 1,
-  "shiten_code": "S01",
+  "shiten_code": "001",
   "shiten_name": "本店営業部",
   "shiten_name_kana": "ホンテンエイギョウブ",
   "kinyu_shiten_flg": false,
@@ -9120,78 +9258,78 @@
 }</t>
         </is>
       </c>
-      <c r="D107" s="10" t="n"/>
-      <c r="E107" s="10" t="n"/>
-      <c r="F107" s="10" t="n"/>
-      <c r="G107" s="10" t="n"/>
-      <c r="H107" s="10" t="n"/>
-      <c r="I107" s="10" t="n"/>
-      <c r="J107" s="10" t="n"/>
-      <c r="K107" s="10" t="n"/>
-      <c r="L107" s="10" t="n"/>
-      <c r="M107" s="10" t="n"/>
-      <c r="N107" s="10" t="n"/>
-      <c r="O107" s="10" t="n"/>
-      <c r="P107" s="10" t="n"/>
-      <c r="Q107" s="10" t="n"/>
-      <c r="R107" s="10" t="n"/>
-      <c r="S107" s="10" t="n"/>
-      <c r="T107" s="10" t="n"/>
-      <c r="U107" s="10" t="n"/>
-      <c r="V107" s="10" t="n"/>
-      <c r="W107" s="10" t="n"/>
-      <c r="X107" s="10" t="n"/>
-      <c r="Y107" s="10" t="n"/>
-      <c r="Z107" s="10" t="n"/>
-      <c r="AA107" s="10" t="n"/>
-      <c r="AB107" s="10" t="n"/>
-      <c r="AC107" s="10" t="n"/>
-      <c r="AD107" s="10" t="n"/>
-      <c r="AE107" s="10" t="n"/>
-      <c r="AF107" s="10" t="n"/>
-      <c r="AG107" s="10" t="n"/>
-      <c r="AH107" s="10" t="n"/>
-      <c r="AI107" s="10" t="n"/>
-      <c r="AJ107" s="10" t="n"/>
-      <c r="AK107" s="11" t="n"/>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="B108" s="27" t="inlineStr">
+      <c r="D118" s="10" t="n"/>
+      <c r="E118" s="10" t="n"/>
+      <c r="F118" s="10" t="n"/>
+      <c r="G118" s="10" t="n"/>
+      <c r="H118" s="10" t="n"/>
+      <c r="I118" s="10" t="n"/>
+      <c r="J118" s="10" t="n"/>
+      <c r="K118" s="10" t="n"/>
+      <c r="L118" s="10" t="n"/>
+      <c r="M118" s="10" t="n"/>
+      <c r="N118" s="10" t="n"/>
+      <c r="O118" s="10" t="n"/>
+      <c r="P118" s="10" t="n"/>
+      <c r="Q118" s="10" t="n"/>
+      <c r="R118" s="10" t="n"/>
+      <c r="S118" s="10" t="n"/>
+      <c r="T118" s="10" t="n"/>
+      <c r="U118" s="10" t="n"/>
+      <c r="V118" s="10" t="n"/>
+      <c r="W118" s="10" t="n"/>
+      <c r="X118" s="10" t="n"/>
+      <c r="Y118" s="10" t="n"/>
+      <c r="Z118" s="10" t="n"/>
+      <c r="AA118" s="10" t="n"/>
+      <c r="AB118" s="10" t="n"/>
+      <c r="AC118" s="10" t="n"/>
+      <c r="AD118" s="10" t="n"/>
+      <c r="AE118" s="10" t="n"/>
+      <c r="AF118" s="10" t="n"/>
+      <c r="AG118" s="10" t="n"/>
+      <c r="AH118" s="10" t="n"/>
+      <c r="AI118" s="10" t="n"/>
+      <c r="AJ118" s="10" t="n"/>
+      <c r="AK118" s="11" t="n"/>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="B119" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="C109" s="41" t="inlineStr">
+    <row r="120" ht="18" customHeight="1">
+      <c r="C120" s="41" t="inlineStr">
         <is>
           <t>登録されたデータをdata オブジェクトとして返却する。HTTP 201。</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="B110" s="27" t="inlineStr">
+    <row r="121" ht="18" customHeight="1">
+      <c r="B121" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="C111" s="41" t="inlineStr">
+    <row r="122" ht="18" customHeight="1">
+      <c r="C122" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="C112" s="41" t="inlineStr">
+    <row r="123" ht="18" customHeight="1">
+      <c r="C123" s="41" t="inlineStr">
         <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="216" customHeight="1">
-      <c r="C113" s="42" t="inlineStr">
+    <row r="124" ht="216" customHeight="1">
+      <c r="C124" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -9207,43 +9345,43 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D113" s="10" t="n"/>
-      <c r="E113" s="10" t="n"/>
-      <c r="F113" s="10" t="n"/>
-      <c r="G113" s="10" t="n"/>
-      <c r="H113" s="10" t="n"/>
-      <c r="I113" s="10" t="n"/>
-      <c r="J113" s="10" t="n"/>
-      <c r="K113" s="10" t="n"/>
-      <c r="L113" s="10" t="n"/>
-      <c r="M113" s="10" t="n"/>
-      <c r="N113" s="10" t="n"/>
-      <c r="O113" s="10" t="n"/>
-      <c r="P113" s="10" t="n"/>
-      <c r="Q113" s="10" t="n"/>
-      <c r="R113" s="10" t="n"/>
-      <c r="S113" s="10" t="n"/>
-      <c r="T113" s="10" t="n"/>
-      <c r="U113" s="10" t="n"/>
-      <c r="V113" s="10" t="n"/>
-      <c r="W113" s="10" t="n"/>
-      <c r="X113" s="10" t="n"/>
-      <c r="Y113" s="10" t="n"/>
-      <c r="Z113" s="10" t="n"/>
-      <c r="AA113" s="10" t="n"/>
-      <c r="AB113" s="10" t="n"/>
-      <c r="AC113" s="10" t="n"/>
-      <c r="AD113" s="10" t="n"/>
-      <c r="AE113" s="10" t="n"/>
-      <c r="AF113" s="10" t="n"/>
-      <c r="AG113" s="10" t="n"/>
-      <c r="AH113" s="10" t="n"/>
-      <c r="AI113" s="10" t="n"/>
-      <c r="AJ113" s="10" t="n"/>
-      <c r="AK113" s="11" t="n"/>
+      <c r="D124" s="10" t="n"/>
+      <c r="E124" s="10" t="n"/>
+      <c r="F124" s="10" t="n"/>
+      <c r="G124" s="10" t="n"/>
+      <c r="H124" s="10" t="n"/>
+      <c r="I124" s="10" t="n"/>
+      <c r="J124" s="10" t="n"/>
+      <c r="K124" s="10" t="n"/>
+      <c r="L124" s="10" t="n"/>
+      <c r="M124" s="10" t="n"/>
+      <c r="N124" s="10" t="n"/>
+      <c r="O124" s="10" t="n"/>
+      <c r="P124" s="10" t="n"/>
+      <c r="Q124" s="10" t="n"/>
+      <c r="R124" s="10" t="n"/>
+      <c r="S124" s="10" t="n"/>
+      <c r="T124" s="10" t="n"/>
+      <c r="U124" s="10" t="n"/>
+      <c r="V124" s="10" t="n"/>
+      <c r="W124" s="10" t="n"/>
+      <c r="X124" s="10" t="n"/>
+      <c r="Y124" s="10" t="n"/>
+      <c r="Z124" s="10" t="n"/>
+      <c r="AA124" s="10" t="n"/>
+      <c r="AB124" s="10" t="n"/>
+      <c r="AC124" s="10" t="n"/>
+      <c r="AD124" s="10" t="n"/>
+      <c r="AE124" s="10" t="n"/>
+      <c r="AF124" s="10" t="n"/>
+      <c r="AG124" s="10" t="n"/>
+      <c r="AH124" s="10" t="n"/>
+      <c r="AI124" s="10" t="n"/>
+      <c r="AJ124" s="10" t="n"/>
+      <c r="AK124" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="270">
+  <mergeCells count="279">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
@@ -9259,7 +9397,6 @@
     <mergeCell ref="B72:I72"/>
     <mergeCell ref="C102:AK102"/>
     <mergeCell ref="D48:L48"/>
-    <mergeCell ref="A76:AK76"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M32:P32"/>
     <mergeCell ref="N18:AK18"/>
@@ -9267,12 +9404,12 @@
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
     <mergeCell ref="Y32:AB32"/>
+    <mergeCell ref="C108:AK108"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="M46:P46"/>
     <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="D82:AK82"/>
     <mergeCell ref="M43:P43"/>
     <mergeCell ref="Y52:AE52"/>
     <mergeCell ref="AF23:AK23"/>
@@ -9281,24 +9418,26 @@
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="C112:AK112"/>
+    <mergeCell ref="C85:AK85"/>
+    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C91:AK91"/>
-    <mergeCell ref="C94:AK94"/>
     <mergeCell ref="C109:AK109"/>
+    <mergeCell ref="C112:AK112"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
     <mergeCell ref="D51:L51"/>
     <mergeCell ref="AF52:AK52"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="B10:I10"/>
+    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
+    <mergeCell ref="D101:AK101"/>
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="M25:P25"/>
@@ -9307,14 +9446,14 @@
     <mergeCell ref="AF49:AK49"/>
     <mergeCell ref="C70:AK70"/>
     <mergeCell ref="T37:X37"/>
-    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="M45:P45"/>
+    <mergeCell ref="B115:AK115"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="A21:AK21"/>
+    <mergeCell ref="B75:I75"/>
     <mergeCell ref="T29:X29"/>
-    <mergeCell ref="B77:AK77"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="M47:P47"/>
@@ -9325,15 +9464,16 @@
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="D47:L47"/>
     <mergeCell ref="AC29:AE29"/>
-    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q44:S44"/>
+    <mergeCell ref="C104:AK104"/>
+    <mergeCell ref="B119:AK119"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="D89:AK89"/>
     <mergeCell ref="AC31:AE31"/>
     <mergeCell ref="AF32:AK32"/>
-    <mergeCell ref="B78:AK78"/>
+    <mergeCell ref="B103:AK103"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="AF41:AK41"/>
@@ -9345,32 +9485,36 @@
     <mergeCell ref="Q48:S48"/>
     <mergeCell ref="D88:AK88"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="C103:AK103"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
+    <mergeCell ref="B78:I78"/>
     <mergeCell ref="C55:AK55"/>
     <mergeCell ref="C99:AK99"/>
+    <mergeCell ref="A82:AK82"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="T40:X40"/>
+    <mergeCell ref="C117:AK117"/>
     <mergeCell ref="C26:L26"/>
-    <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y39:AE39"/>
+    <mergeCell ref="D90:AK90"/>
     <mergeCell ref="M51:P51"/>
-    <mergeCell ref="B95:AK95"/>
+    <mergeCell ref="C118:AK118"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="B104:AK104"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="AF33:AK33"/>
+    <mergeCell ref="B97:AK97"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C61:AK61"/>
+    <mergeCell ref="D107:AK107"/>
     <mergeCell ref="T46:X46"/>
+    <mergeCell ref="C122:AK122"/>
     <mergeCell ref="B63:I63"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="M27:P27"/>
@@ -9399,15 +9543,16 @@
     <mergeCell ref="C37:L37"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="D92:AK92"/>
+    <mergeCell ref="M50:P50"/>
     <mergeCell ref="C98:AK98"/>
-    <mergeCell ref="M50:P50"/>
-    <mergeCell ref="C107:AK107"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="Q49:S49"/>
     <mergeCell ref="T50:X50"/>
+    <mergeCell ref="C116:AK116"/>
     <mergeCell ref="T44:X44"/>
     <mergeCell ref="C64:AK64"/>
     <mergeCell ref="C30:L30"/>
@@ -9416,11 +9561,12 @@
     <mergeCell ref="Y43:AE43"/>
     <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
+    <mergeCell ref="D94:AK94"/>
     <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="B108:AK108"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
+    <mergeCell ref="B84:AK84"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
@@ -9429,17 +9575,17 @@
     <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="T41:X41"/>
-    <mergeCell ref="D80:AK80"/>
+    <mergeCell ref="C105:AK105"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="Y44:AE44"/>
-    <mergeCell ref="C105:AK105"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="AC32:AE32"/>
+    <mergeCell ref="C120:AK120"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="T43:X43"/>
     <mergeCell ref="Y31:AB31"/>
@@ -9453,12 +9599,13 @@
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="C67:AK67"/>
+    <mergeCell ref="B121:AK121"/>
     <mergeCell ref="Y46:AE46"/>
+    <mergeCell ref="D91:AK91"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="M41:P41"/>
-    <mergeCell ref="C111:AK111"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="B14:I19"/>
@@ -9469,44 +9616,44 @@
     <mergeCell ref="Y48:AE48"/>
     <mergeCell ref="D93:AK93"/>
     <mergeCell ref="AC26:AE26"/>
-    <mergeCell ref="C92:AK92"/>
+    <mergeCell ref="D106:AK106"/>
+    <mergeCell ref="B111:AK111"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="A35:AK35"/>
     <mergeCell ref="D43:L43"/>
-    <mergeCell ref="D83:AK83"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="Y42:AE42"/>
-    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="Y47:AE47"/>
     <mergeCell ref="B60:I60"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="D85:AK85"/>
     <mergeCell ref="B57:I57"/>
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="AC27:AE27"/>
+    <mergeCell ref="B83:AK83"/>
+    <mergeCell ref="C124:AK124"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="D50:L50"/>
-    <mergeCell ref="D84:AK84"/>
     <mergeCell ref="D44:L44"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="C90:AK90"/>
     <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="B110:AK110"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="D86:AK86"/>
+    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="Y50:AE50"/>
+    <mergeCell ref="D95:AK95"/>
     <mergeCell ref="AC28:AE28"/>
+    <mergeCell ref="C76:AK76"/>
     <mergeCell ref="M30:P30"/>
-    <mergeCell ref="B100:AK100"/>
+    <mergeCell ref="C110:AK110"/>
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="D45:L45"/>
@@ -9525,7 +9672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK115"/>
+  <dimension ref="A1:AK127"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -9686,7 +9833,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -10631,7 +10778,7 @@
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>管理支店ID</t>
+          <t>管理支店ID（m_kanri_shitenに存在し、対象支店と同一JAに属すること）</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -10700,7 +10847,7 @@
       <c r="AJ28" s="10" t="n"/>
       <c r="AK28" s="11" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1">
+    <row r="29" ht="36" customHeight="1">
       <c r="B29" s="31" t="n">
         <v>6</v>
       </c>
@@ -10735,7 +10882,7 @@
       <c r="S29" s="11" t="n"/>
       <c r="T29" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>△※</t>
         </is>
       </c>
       <c r="U29" s="10" t="n"/>
@@ -10753,7 +10900,7 @@
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>JASTEM_データ送信取扱店舗コード※空文字許容</t>
+          <t>JASTEM_データ送信取扱店舗コード。kinyu_shiten_flg=true 時は必須（必須項目です。）、false 時は空文字許容</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -10762,7 +10909,7 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1">
+    <row r="30" ht="36" customHeight="1">
       <c r="B30" s="31" t="n">
         <v>7</v>
       </c>
@@ -10797,7 +10944,7 @@
       <c r="S30" s="11" t="n"/>
       <c r="T30" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>△※</t>
         </is>
       </c>
       <c r="U30" s="10" t="n"/>
@@ -10815,7 +10962,7 @@
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>JASTEM_店舗名※空文字許容</t>
+          <t>JASTEM_店舗名。kinyu_shiten_flg=true 時は必須（必須項目です。）、false 時は空文字許容</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -10824,7 +10971,7 @@
       <c r="AJ30" s="10" t="n"/>
       <c r="AK30" s="11" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1">
+    <row r="31" ht="36" customHeight="1">
       <c r="B31" s="31" t="n">
         <v>8</v>
       </c>
@@ -10859,7 +11006,7 @@
       <c r="S31" s="11" t="n"/>
       <c r="T31" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>△※</t>
         </is>
       </c>
       <c r="U31" s="10" t="n"/>
@@ -10877,7 +11024,7 @@
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>JASTEM_貯金種別※空文字許容</t>
+          <t>JASTEM_貯金種別。kinyu_shiten_flg=true 時は必須（必須項目です。）、false 時は空文字許容</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -10886,7 +11033,7 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1">
+    <row r="32" ht="36" customHeight="1">
       <c r="B32" s="31" t="n">
         <v>9</v>
       </c>
@@ -10921,7 +11068,7 @@
       <c r="S32" s="11" t="n"/>
       <c r="T32" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>△※</t>
         </is>
       </c>
       <c r="U32" s="10" t="n"/>
@@ -10939,7 +11086,7 @@
       <c r="AE32" s="11" t="n"/>
       <c r="AF32" s="19" t="inlineStr">
         <is>
-          <t>JASTEM_口座番号※空文字許容</t>
+          <t>JASTEM_口座番号。kinyu_shiten_flg=true 時は必須（必須項目です。）、false 時は空文字許容</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -10994,7 +11141,9 @@
       <c r="Z33" s="10" t="n"/>
       <c r="AA33" s="10" t="n"/>
       <c r="AB33" s="11" t="n"/>
-      <c r="AC33" s="17" t="inlineStr"/>
+      <c r="AC33" s="17" t="n">
+        <v>500</v>
+      </c>
       <c r="AD33" s="10" t="n"/>
       <c r="AE33" s="11" t="n"/>
       <c r="AF33" s="19" t="inlineStr">
@@ -12066,7 +12215,7 @@
   "data": {
     "shiten_id": 1,
     "ja_id": 1,
-    "shiten_code": "S01",
+    "shiten_code": "001",
     "shiten_name": "本店営業部（名称変更）",
     "shiten_name_kana": "ホンテンエイギョウブ",
     "kinyu_shiten_flg": true,
@@ -12129,8 +12278,8 @@
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
-  "message": "入力値が不正です。詳細はerrorsフィールドを確認してください",
-  "errors": [{ "field": "shiten_name", "message": "支店名は必須です" }]
+  "message": "入力値が不正です。詳細はerrorsフィールドを確認してください。",
+  "errors": [{ "field": "shiten_name", "message": "支店名を入力してください。" }]
 }</t>
         </is>
       </c>
@@ -12181,7 +12330,7 @@
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
-  "message": "セッションが切れました。再度ログインしてください"
+  "message": "セッションが切れました。再度ログインしてください。"
 }</t>
         </is>
       </c>
@@ -12232,7 +12381,7 @@
         <is>
           <t>{
   "error_code": "FORBIDDEN",
-  "message": "この画面へのアクセス権限がありません"
+  "message": "この画面へのアクセス権限がありません。"
 }</t>
         </is>
       </c>
@@ -12283,7 +12432,7 @@
         <is>
           <t>{
   "error_code": "NOT_FOUND",
-  "message": "指定された支店が見つかりません"
+  "message": "指定された支店が見つかりません。"
 }</t>
         </is>
       </c>
@@ -12325,7 +12474,7 @@
     <row r="72" ht="19.5" customHeight="1">
       <c r="B72" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 500 Internal Server Error）</t>
+          <t>レスポンス（失敗 400 Bad Request（管理支店IDが存在しない場合））</t>
         </is>
       </c>
     </row>
@@ -12333,8 +12482,8 @@
       <c r="C73" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "INTERNAL_SERVER_ERROR",
-  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+  "error_code": "BAD_REQUEST",
+  "message": "管理支店IDが存在しません。"
 }</t>
         </is>
       </c>
@@ -12373,207 +12522,316 @@
       <c r="AJ73" s="10" t="n"/>
       <c r="AK73" s="11" t="n"/>
     </row>
-    <row r="75" ht="19.5" customHeight="1"/>
-    <row r="76" ht="19.5" customHeight="1">
-      <c r="A76" s="27" t="inlineStr">
+    <row r="75" ht="19.5" customHeight="1">
+      <c r="B75" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 403 Forbidden（管理支店IDが別JAに属する場合））</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="72" customHeight="1">
+      <c r="C76" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "DATA_SCOPE_VIOLATION",
+  "message": "このデータへのアクセス権限がありません。"
+}</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="10" t="n"/>
+      <c r="J76" s="10" t="n"/>
+      <c r="K76" s="10" t="n"/>
+      <c r="L76" s="10" t="n"/>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="10" t="n"/>
+      <c r="Q76" s="10" t="n"/>
+      <c r="R76" s="10" t="n"/>
+      <c r="S76" s="10" t="n"/>
+      <c r="T76" s="10" t="n"/>
+      <c r="U76" s="10" t="n"/>
+      <c r="V76" s="10" t="n"/>
+      <c r="W76" s="10" t="n"/>
+      <c r="X76" s="10" t="n"/>
+      <c r="Y76" s="10" t="n"/>
+      <c r="Z76" s="10" t="n"/>
+      <c r="AA76" s="10" t="n"/>
+      <c r="AB76" s="10" t="n"/>
+      <c r="AC76" s="10" t="n"/>
+      <c r="AD76" s="10" t="n"/>
+      <c r="AE76" s="10" t="n"/>
+      <c r="AF76" s="10" t="n"/>
+      <c r="AG76" s="10" t="n"/>
+      <c r="AH76" s="10" t="n"/>
+      <c r="AI76" s="10" t="n"/>
+      <c r="AJ76" s="10" t="n"/>
+      <c r="AK76" s="11" t="n"/>
+    </row>
+    <row r="78" ht="19.5" customHeight="1">
+      <c r="B78" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 500 Internal Server Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="72" customHeight="1">
+      <c r="C79" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "INTERNAL_SERVER_ERROR",
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください。"
+}</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="10" t="n"/>
+      <c r="J79" s="10" t="n"/>
+      <c r="K79" s="10" t="n"/>
+      <c r="L79" s="10" t="n"/>
+      <c r="M79" s="10" t="n"/>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="10" t="n"/>
+      <c r="Q79" s="10" t="n"/>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="10" t="n"/>
+      <c r="T79" s="10" t="n"/>
+      <c r="U79" s="10" t="n"/>
+      <c r="V79" s="10" t="n"/>
+      <c r="W79" s="10" t="n"/>
+      <c r="X79" s="10" t="n"/>
+      <c r="Y79" s="10" t="n"/>
+      <c r="Z79" s="10" t="n"/>
+      <c r="AA79" s="10" t="n"/>
+      <c r="AB79" s="10" t="n"/>
+      <c r="AC79" s="10" t="n"/>
+      <c r="AD79" s="10" t="n"/>
+      <c r="AE79" s="10" t="n"/>
+      <c r="AF79" s="10" t="n"/>
+      <c r="AG79" s="10" t="n"/>
+      <c r="AH79" s="10" t="n"/>
+      <c r="AI79" s="10" t="n"/>
+      <c r="AJ79" s="10" t="n"/>
+      <c r="AK79" s="11" t="n"/>
+    </row>
+    <row r="81" ht="19.5" customHeight="1"/>
+    <row r="82" ht="19.5" customHeight="1">
+      <c r="A82" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="54" customHeight="1">
-      <c r="B77" s="42" t="inlineStr">
+    <row r="83" ht="54" customHeight="1">
+      <c r="B83" s="42" t="inlineStr">
         <is>
           <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
 いずれかが失敗した場合は全てロールバックすること。
 例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
         </is>
       </c>
-      <c r="C77" s="10" t="n"/>
-      <c r="D77" s="10" t="n"/>
-      <c r="E77" s="10" t="n"/>
-      <c r="F77" s="10" t="n"/>
-      <c r="G77" s="10" t="n"/>
-      <c r="H77" s="10" t="n"/>
-      <c r="I77" s="10" t="n"/>
-      <c r="J77" s="10" t="n"/>
-      <c r="K77" s="10" t="n"/>
-      <c r="L77" s="10" t="n"/>
-      <c r="M77" s="10" t="n"/>
-      <c r="N77" s="10" t="n"/>
-      <c r="O77" s="10" t="n"/>
-      <c r="P77" s="10" t="n"/>
-      <c r="Q77" s="10" t="n"/>
-      <c r="R77" s="10" t="n"/>
-      <c r="S77" s="10" t="n"/>
-      <c r="T77" s="10" t="n"/>
-      <c r="U77" s="10" t="n"/>
-      <c r="V77" s="10" t="n"/>
-      <c r="W77" s="10" t="n"/>
-      <c r="X77" s="10" t="n"/>
-      <c r="Y77" s="10" t="n"/>
-      <c r="Z77" s="10" t="n"/>
-      <c r="AA77" s="10" t="n"/>
-      <c r="AB77" s="10" t="n"/>
-      <c r="AC77" s="10" t="n"/>
-      <c r="AD77" s="10" t="n"/>
-      <c r="AE77" s="10" t="n"/>
-      <c r="AF77" s="10" t="n"/>
-      <c r="AG77" s="10" t="n"/>
-      <c r="AH77" s="10" t="n"/>
-      <c r="AI77" s="10" t="n"/>
-      <c r="AJ77" s="10" t="n"/>
-      <c r="AK77" s="11" t="n"/>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="B78" s="27" t="inlineStr">
+      <c r="C83" s="10" t="n"/>
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
+      <c r="H83" s="10" t="n"/>
+      <c r="I83" s="10" t="n"/>
+      <c r="J83" s="10" t="n"/>
+      <c r="K83" s="10" t="n"/>
+      <c r="L83" s="10" t="n"/>
+      <c r="M83" s="10" t="n"/>
+      <c r="N83" s="10" t="n"/>
+      <c r="O83" s="10" t="n"/>
+      <c r="P83" s="10" t="n"/>
+      <c r="Q83" s="10" t="n"/>
+      <c r="R83" s="10" t="n"/>
+      <c r="S83" s="10" t="n"/>
+      <c r="T83" s="10" t="n"/>
+      <c r="U83" s="10" t="n"/>
+      <c r="V83" s="10" t="n"/>
+      <c r="W83" s="10" t="n"/>
+      <c r="X83" s="10" t="n"/>
+      <c r="Y83" s="10" t="n"/>
+      <c r="Z83" s="10" t="n"/>
+      <c r="AA83" s="10" t="n"/>
+      <c r="AB83" s="10" t="n"/>
+      <c r="AC83" s="10" t="n"/>
+      <c r="AD83" s="10" t="n"/>
+      <c r="AE83" s="10" t="n"/>
+      <c r="AF83" s="10" t="n"/>
+      <c r="AG83" s="10" t="n"/>
+      <c r="AH83" s="10" t="n"/>
+      <c r="AI83" s="10" t="n"/>
+      <c r="AJ83" s="10" t="n"/>
+      <c r="AK83" s="11" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="B84" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="C79" s="41" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="C85" s="41" t="inlineStr">
         <is>
           <t>パスパラメータ：shiten_id 数値型チェック、必須</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="C80" s="41" t="inlineStr">
+    <row r="86" ht="18" customHeight="1">
+      <c r="C86" s="41" t="inlineStr">
         <is>
           <t>リクエストボディ：</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="D81" s="41" t="inlineStr">
-        <is>
-          <t>shiten_name：必須、最大100桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="D82" s="41" t="inlineStr">
-        <is>
-          <t>shiten_name_kana：任意、最大100桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="D83" s="41" t="inlineStr">
-        <is>
-          <t>kanri_shiten_id：必須、数値型チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="D84" s="41" t="inlineStr">
-        <is>
-          <t>kinyu_shiten_flg：任意、ブール値</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="D85" s="41" t="inlineStr">
-        <is>
-          <t>jastem_toriatsukai_tenpo_code：任意、最大3桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="D86" s="41" t="inlineStr">
-        <is>
-          <t>jastem_tenpo_name：任意、最大15桁</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="D87" s="41" t="inlineStr">
         <is>
-          <t>jastem_tyokin_shubetsu：任意、最大1桁</t>
+          <t>shiten_name：必須、最大100桁</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="D88" s="41" t="inlineStr">
         <is>
-          <t>jastem_koza_no：任意、最大7桁</t>
+          <t>shiten_name_kana：任意、最大100桁</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="D89" s="41" t="inlineStr">
         <is>
+          <t>kanri_shiten_id：必須、数値型チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="D90" s="41" t="inlineStr">
+        <is>
+          <t>kinyu_shiten_flg：任意、ブール値</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="D91" s="41" t="inlineStr">
+        <is>
+          <t>jastem_toriatsukai_tenpo_code：任意、最大3桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="D92" s="41" t="inlineStr">
+        <is>
+          <t>jastem_tenpo_name：任意、最大15桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="D93" s="41" t="inlineStr">
+        <is>
+          <t>jastem_tyokin_shubetsu：任意、最大1桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="D94" s="41" t="inlineStr">
+        <is>
+          <t>jastem_koza_no：任意、最大7桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="D95" s="41" t="inlineStr">
+        <is>
           <t>biko：任意、文字列</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="36" customHeight="1">
-      <c r="C90" s="41" t="inlineStr">
+    <row r="96" ht="36" customHeight="1">
+      <c r="C96" s="41" t="inlineStr">
         <is>
           <t>バリデーションエラーの場合：HTTP 400 (`VALIDATION_ERROR`) + errors配列</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="B91" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="C92" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="C93" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：`shiten.update` を保持しているか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="36" customHeight="1">
-      <c r="D94" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="C95" s="41" t="inlineStr">
-        <is>
-          <t>フィールドレベル制限：ロールに応じて編集可能なフィールドをフィルタリングする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="90" customHeight="1">
-      <c r="D96" s="41" t="inlineStr">
-        <is>
-          <t>CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN : shiten_name, shiten_name_kana, kinyu_shiten_flg, jastem_toriatsukai_tenpo_code, jastem_tenpo_name, jastem_tyokin_shubetsu, jastem_koza_no, kanri_shiten_id, biko のみ更新可能</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="B97" s="27" t="inlineStr">
         <is>
-          <t>4.3 対象レコードの存在確認</t>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="C98" s="41" t="inlineStr">
         <is>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="C99" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：`shiten.update` を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="36" customHeight="1">
+      <c r="D100" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="C101" s="41" t="inlineStr">
+        <is>
+          <t>フィールドレベル制限：ロールに応じて編集可能なフィールドをフィルタリングする</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="36" customHeight="1">
+      <c r="D102" s="41" t="inlineStr">
+        <is>
+          <t>NICHINO_ADMIN / NICHINO_STAFF / CHUOKAI / JA_HONTEN：全カラム編集可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="D103" s="41" t="inlineStr">
+        <is>
+          <t>JA_KANRI_SHITEN：`kanri_shiten_id` 以外の全カラムのみ編集可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="B104" s="27" t="inlineStr">
+        <is>
+          <t>4.3 対象レコードの存在確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="C105" s="41" t="inlineStr">
+        <is>
           <t>ログインユーザーのスコープを取得する（ja_id）。</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="162" customHeight="1">
-      <c r="C99" s="42" t="inlineStr">
+    <row r="106" ht="144" customHeight="1">
+      <c r="C106" s="42" t="inlineStr">
         <is>
           <t>SELECT shiten_id, ja_id, shiten_code, shiten_name, shiten_name_kana,
        kinyu_shiten_flg,
@@ -12582,68 +12840,102 @@
        kanri_shiten_id, biko, created_at, updated_at
 FROM m_shiten
 WHERE shiten_id = :shiten_id
-  AND ja_id = :ja_id
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D99" s="10" t="n"/>
-      <c r="E99" s="10" t="n"/>
-      <c r="F99" s="10" t="n"/>
-      <c r="G99" s="10" t="n"/>
-      <c r="H99" s="10" t="n"/>
-      <c r="I99" s="10" t="n"/>
-      <c r="J99" s="10" t="n"/>
-      <c r="K99" s="10" t="n"/>
-      <c r="L99" s="10" t="n"/>
-      <c r="M99" s="10" t="n"/>
-      <c r="N99" s="10" t="n"/>
-      <c r="O99" s="10" t="n"/>
-      <c r="P99" s="10" t="n"/>
-      <c r="Q99" s="10" t="n"/>
-      <c r="R99" s="10" t="n"/>
-      <c r="S99" s="10" t="n"/>
-      <c r="T99" s="10" t="n"/>
-      <c r="U99" s="10" t="n"/>
-      <c r="V99" s="10" t="n"/>
-      <c r="W99" s="10" t="n"/>
-      <c r="X99" s="10" t="n"/>
-      <c r="Y99" s="10" t="n"/>
-      <c r="Z99" s="10" t="n"/>
-      <c r="AA99" s="10" t="n"/>
-      <c r="AB99" s="10" t="n"/>
-      <c r="AC99" s="10" t="n"/>
-      <c r="AD99" s="10" t="n"/>
-      <c r="AE99" s="10" t="n"/>
-      <c r="AF99" s="10" t="n"/>
-      <c r="AG99" s="10" t="n"/>
-      <c r="AH99" s="10" t="n"/>
-      <c r="AI99" s="10" t="n"/>
-      <c r="AJ99" s="10" t="n"/>
-      <c r="AK99" s="11" t="n"/>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="C100" s="41" t="inlineStr">
+      <c r="D106" s="10" t="n"/>
+      <c r="E106" s="10" t="n"/>
+      <c r="F106" s="10" t="n"/>
+      <c r="G106" s="10" t="n"/>
+      <c r="H106" s="10" t="n"/>
+      <c r="I106" s="10" t="n"/>
+      <c r="J106" s="10" t="n"/>
+      <c r="K106" s="10" t="n"/>
+      <c r="L106" s="10" t="n"/>
+      <c r="M106" s="10" t="n"/>
+      <c r="N106" s="10" t="n"/>
+      <c r="O106" s="10" t="n"/>
+      <c r="P106" s="10" t="n"/>
+      <c r="Q106" s="10" t="n"/>
+      <c r="R106" s="10" t="n"/>
+      <c r="S106" s="10" t="n"/>
+      <c r="T106" s="10" t="n"/>
+      <c r="U106" s="10" t="n"/>
+      <c r="V106" s="10" t="n"/>
+      <c r="W106" s="10" t="n"/>
+      <c r="X106" s="10" t="n"/>
+      <c r="Y106" s="10" t="n"/>
+      <c r="Z106" s="10" t="n"/>
+      <c r="AA106" s="10" t="n"/>
+      <c r="AB106" s="10" t="n"/>
+      <c r="AC106" s="10" t="n"/>
+      <c r="AD106" s="10" t="n"/>
+      <c r="AE106" s="10" t="n"/>
+      <c r="AF106" s="10" t="n"/>
+      <c r="AG106" s="10" t="n"/>
+      <c r="AH106" s="10" t="n"/>
+      <c r="AI106" s="10" t="n"/>
+      <c r="AJ106" s="10" t="n"/>
+      <c r="AK106" s="11" t="n"/>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="C107" s="41" t="inlineStr">
         <is>
           <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="C101" s="41" t="inlineStr">
-        <is>
-          <t>ja_id が一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="B102" s="27" t="inlineStr">
+    <row r="108" ht="18" customHeight="1">
+      <c r="C108" s="41" t="inlineStr">
+        <is>
+          <t>レコードは存在するが `ja_id` がログインユーザーのスコープと一致しない場合も</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="36" customHeight="1">
+      <c r="C109" s="41" t="inlineStr">
+        <is>
+          <t>同一JA内であっても、JA_KANRI_SHITEN が自身の `kanri_shiten_id` に属さない支店</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="C110" s="41" t="inlineStr">
+        <is>
+          <t>`kinyu_shiten_flg` がリクエストに含まれ、かつ既存値と異なる場合：HTTP 400</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="36" customHeight="1">
+      <c r="C111" s="41" t="inlineStr">
+        <is>
+          <t>kanri_shiten_id がリクエストに含まれる場合、その値が m_kanri_shiten に存在し、</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="36" customHeight="1">
+      <c r="D112" s="41" t="inlineStr">
+        <is>
+          <t>レコードが存在しない場合：HTTP 400 (`BAD_REQUEST`) `管理支店IDが存在しません。`</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="36" customHeight="1">
+      <c r="D113" s="41" t="inlineStr">
+        <is>
+          <t>レコードは存在するが JA が異なる場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="B114" s="27" t="inlineStr">
         <is>
           <t>4.4 データ更新</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="288" customHeight="1">
-      <c r="C103" s="42" t="inlineStr">
+    <row r="115" ht="288" customHeight="1">
+      <c r="C115" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_shiten
 SET shiten_name = :shiten_name,
@@ -12661,276 +12953,6 @@
   AND ja_id = :ja_id
   AND deleted_at IS NULL
 RETURNING *</t>
-        </is>
-      </c>
-      <c r="D103" s="10" t="n"/>
-      <c r="E103" s="10" t="n"/>
-      <c r="F103" s="10" t="n"/>
-      <c r="G103" s="10" t="n"/>
-      <c r="H103" s="10" t="n"/>
-      <c r="I103" s="10" t="n"/>
-      <c r="J103" s="10" t="n"/>
-      <c r="K103" s="10" t="n"/>
-      <c r="L103" s="10" t="n"/>
-      <c r="M103" s="10" t="n"/>
-      <c r="N103" s="10" t="n"/>
-      <c r="O103" s="10" t="n"/>
-      <c r="P103" s="10" t="n"/>
-      <c r="Q103" s="10" t="n"/>
-      <c r="R103" s="10" t="n"/>
-      <c r="S103" s="10" t="n"/>
-      <c r="T103" s="10" t="n"/>
-      <c r="U103" s="10" t="n"/>
-      <c r="V103" s="10" t="n"/>
-      <c r="W103" s="10" t="n"/>
-      <c r="X103" s="10" t="n"/>
-      <c r="Y103" s="10" t="n"/>
-      <c r="Z103" s="10" t="n"/>
-      <c r="AA103" s="10" t="n"/>
-      <c r="AB103" s="10" t="n"/>
-      <c r="AC103" s="10" t="n"/>
-      <c r="AD103" s="10" t="n"/>
-      <c r="AE103" s="10" t="n"/>
-      <c r="AF103" s="10" t="n"/>
-      <c r="AG103" s="10" t="n"/>
-      <c r="AH103" s="10" t="n"/>
-      <c r="AI103" s="10" t="n"/>
-      <c r="AJ103" s="10" t="n"/>
-      <c r="AK103" s="11" t="n"/>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="B104" s="27" t="inlineStr">
-        <is>
-          <t>4.5 操作ログ記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="C105" s="41" t="inlineStr">
-        <is>
-          <t>更新前データを取得（4.3 のSELECT結果）し、`before_value` に格納する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="C106" s="41" t="inlineStr">
-        <is>
-          <t>以下のSQLを実行して操作ログを記録する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="216" customHeight="1">
-      <c r="C107" s="42" t="inlineStr">
-        <is>
-          <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
-                   gamen_name, operation, result_status,
-                   target_id, target_table,
-                   before_value, after_value,
-                   error_message, stack_trace,
-                   ip_address, user_agent)
-VALUES (1, NOW(), :account_id, :ja_id,
-        '支店マスタ登録画面 (ACSMS-SCR-007)', 'UPDATE', 1,
-        :shiten_id, 'm_shiten',
-        :before_value_json, :after_value_json,
-        '', '',
-        :ip_address, :user_agent)</t>
-        </is>
-      </c>
-      <c r="D107" s="10" t="n"/>
-      <c r="E107" s="10" t="n"/>
-      <c r="F107" s="10" t="n"/>
-      <c r="G107" s="10" t="n"/>
-      <c r="H107" s="10" t="n"/>
-      <c r="I107" s="10" t="n"/>
-      <c r="J107" s="10" t="n"/>
-      <c r="K107" s="10" t="n"/>
-      <c r="L107" s="10" t="n"/>
-      <c r="M107" s="10" t="n"/>
-      <c r="N107" s="10" t="n"/>
-      <c r="O107" s="10" t="n"/>
-      <c r="P107" s="10" t="n"/>
-      <c r="Q107" s="10" t="n"/>
-      <c r="R107" s="10" t="n"/>
-      <c r="S107" s="10" t="n"/>
-      <c r="T107" s="10" t="n"/>
-      <c r="U107" s="10" t="n"/>
-      <c r="V107" s="10" t="n"/>
-      <c r="W107" s="10" t="n"/>
-      <c r="X107" s="10" t="n"/>
-      <c r="Y107" s="10" t="n"/>
-      <c r="Z107" s="10" t="n"/>
-      <c r="AA107" s="10" t="n"/>
-      <c r="AB107" s="10" t="n"/>
-      <c r="AC107" s="10" t="n"/>
-      <c r="AD107" s="10" t="n"/>
-      <c r="AE107" s="10" t="n"/>
-      <c r="AF107" s="10" t="n"/>
-      <c r="AG107" s="10" t="n"/>
-      <c r="AH107" s="10" t="n"/>
-      <c r="AI107" s="10" t="n"/>
-      <c r="AJ107" s="10" t="n"/>
-      <c r="AK107" s="11" t="n"/>
-    </row>
-    <row r="108" ht="288" customHeight="1">
-      <c r="C108" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：更新前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
-{
-  "shiten_id": 1,
-  "ja_id": 1,
-  "shiten_code": "S01",
-  "shiten_name": "本店営業部",
-  "shiten_name_kana": "ホンテンエイギョウブ",
-  "kinyu_shiten_flg": false,
-  "jastem_toriatsukai_tenpo_code": "001",
-  "jastem_tenpo_name": "本店",
-  "jastem_tyokin_shubetsu": "1",
-  "jastem_koza_no": "1234567",
-  "kanri_shiten_id": 1,
-  "biko": "本店ビル1F"
-}</t>
-        </is>
-      </c>
-      <c r="D108" s="10" t="n"/>
-      <c r="E108" s="10" t="n"/>
-      <c r="F108" s="10" t="n"/>
-      <c r="G108" s="10" t="n"/>
-      <c r="H108" s="10" t="n"/>
-      <c r="I108" s="10" t="n"/>
-      <c r="J108" s="10" t="n"/>
-      <c r="K108" s="10" t="n"/>
-      <c r="L108" s="10" t="n"/>
-      <c r="M108" s="10" t="n"/>
-      <c r="N108" s="10" t="n"/>
-      <c r="O108" s="10" t="n"/>
-      <c r="P108" s="10" t="n"/>
-      <c r="Q108" s="10" t="n"/>
-      <c r="R108" s="10" t="n"/>
-      <c r="S108" s="10" t="n"/>
-      <c r="T108" s="10" t="n"/>
-      <c r="U108" s="10" t="n"/>
-      <c r="V108" s="10" t="n"/>
-      <c r="W108" s="10" t="n"/>
-      <c r="X108" s="10" t="n"/>
-      <c r="Y108" s="10" t="n"/>
-      <c r="Z108" s="10" t="n"/>
-      <c r="AA108" s="10" t="n"/>
-      <c r="AB108" s="10" t="n"/>
-      <c r="AC108" s="10" t="n"/>
-      <c r="AD108" s="10" t="n"/>
-      <c r="AE108" s="10" t="n"/>
-      <c r="AF108" s="10" t="n"/>
-      <c r="AG108" s="10" t="n"/>
-      <c r="AH108" s="10" t="n"/>
-      <c r="AI108" s="10" t="n"/>
-      <c r="AJ108" s="10" t="n"/>
-      <c r="AK108" s="11" t="n"/>
-    </row>
-    <row r="109" ht="288" customHeight="1">
-      <c r="C109" s="42" t="inlineStr">
-        <is>
-          <t>`after_value`：更新後のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
-{
-  "shiten_id": 1,
-  "ja_id": 1,
-  "shiten_code": "S01",
-  "shiten_name": "本店営業部（名称変更）",
-  "shiten_name_kana": "ホンテンエイギョウブ",
-  "kinyu_shiten_flg": true,
-  "jastem_toriatsukai_tenpo_code": "001",
-  "jastem_tenpo_name": "本店",
-  "jastem_tyokin_shubetsu": "1",
-  "jastem_koza_no": "1234567",
-  "kanri_shiten_id": 1,
-  "biko": "本店ビル1F 改装済み"
-}</t>
-        </is>
-      </c>
-      <c r="D109" s="10" t="n"/>
-      <c r="E109" s="10" t="n"/>
-      <c r="F109" s="10" t="n"/>
-      <c r="G109" s="10" t="n"/>
-      <c r="H109" s="10" t="n"/>
-      <c r="I109" s="10" t="n"/>
-      <c r="J109" s="10" t="n"/>
-      <c r="K109" s="10" t="n"/>
-      <c r="L109" s="10" t="n"/>
-      <c r="M109" s="10" t="n"/>
-      <c r="N109" s="10" t="n"/>
-      <c r="O109" s="10" t="n"/>
-      <c r="P109" s="10" t="n"/>
-      <c r="Q109" s="10" t="n"/>
-      <c r="R109" s="10" t="n"/>
-      <c r="S109" s="10" t="n"/>
-      <c r="T109" s="10" t="n"/>
-      <c r="U109" s="10" t="n"/>
-      <c r="V109" s="10" t="n"/>
-      <c r="W109" s="10" t="n"/>
-      <c r="X109" s="10" t="n"/>
-      <c r="Y109" s="10" t="n"/>
-      <c r="Z109" s="10" t="n"/>
-      <c r="AA109" s="10" t="n"/>
-      <c r="AB109" s="10" t="n"/>
-      <c r="AC109" s="10" t="n"/>
-      <c r="AD109" s="10" t="n"/>
-      <c r="AE109" s="10" t="n"/>
-      <c r="AF109" s="10" t="n"/>
-      <c r="AG109" s="10" t="n"/>
-      <c r="AH109" s="10" t="n"/>
-      <c r="AI109" s="10" t="n"/>
-      <c r="AJ109" s="10" t="n"/>
-      <c r="AK109" s="11" t="n"/>
-    </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="B110" s="27" t="inlineStr">
-        <is>
-          <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="C111" s="41" t="inlineStr">
-        <is>
-          <t>更新されたデータをdata オブジェクトとして返却する。HTTP 200。</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="B112" s="27" t="inlineStr">
-        <is>
-          <t>4.7 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="C113" s="41" t="inlineStr">
-        <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="C114" s="41" t="inlineStr">
-        <is>
-          <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="216" customHeight="1">
-      <c r="C115" s="42" t="inlineStr">
-        <is>
-          <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
-                   gamen_name, operation, result_status,
-                   target_id, target_table,
-                   before_value, after_value,
-                   error_message, stack_trace,
-                   ip_address, user_agent)
-VALUES (3, NOW(), :account_id, :ja_id,
-        '支店マスタ登録画面 (ACSMS-SCR-007)', 'UPDATE', 2,
-        :shiten_id, 'm_shiten',
-        '', '',
-        :error_message, :stack_trace,
-        :ip_address, :user_agent)</t>
         </is>
       </c>
       <c r="D115" s="10" t="n"/>
@@ -12968,9 +12990,278 @@
       <c r="AJ115" s="10" t="n"/>
       <c r="AK115" s="11" t="n"/>
     </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="B116" s="27" t="inlineStr">
+        <is>
+          <t>4.5 操作ログ記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="C117" s="41" t="inlineStr">
+        <is>
+          <t>更新前データを取得（4.3 のSELECT結果）し、`before_value` に格納する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="C118" s="41" t="inlineStr">
+        <is>
+          <t>以下のSQLを実行して操作ログを記録する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="216" customHeight="1">
+      <c r="C119" s="42" t="inlineStr">
+        <is>
+          <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
+                   gamen_name, operation, result_status,
+                   target_id, target_table,
+                   before_value, after_value,
+                   error_message, stack_trace,
+                   ip_address, user_agent)
+VALUES (1, NOW(), :account_id, :ja_id,
+        '支店マスタ登録画面 (ACSMS-SCR-007)', 'UPDATE', 1,
+        :shiten_id, 'm_shiten',
+        :before_value_json, :after_value_json,
+        '', '',
+        :ip_address, :user_agent)</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="n"/>
+      <c r="E119" s="10" t="n"/>
+      <c r="F119" s="10" t="n"/>
+      <c r="G119" s="10" t="n"/>
+      <c r="H119" s="10" t="n"/>
+      <c r="I119" s="10" t="n"/>
+      <c r="J119" s="10" t="n"/>
+      <c r="K119" s="10" t="n"/>
+      <c r="L119" s="10" t="n"/>
+      <c r="M119" s="10" t="n"/>
+      <c r="N119" s="10" t="n"/>
+      <c r="O119" s="10" t="n"/>
+      <c r="P119" s="10" t="n"/>
+      <c r="Q119" s="10" t="n"/>
+      <c r="R119" s="10" t="n"/>
+      <c r="S119" s="10" t="n"/>
+      <c r="T119" s="10" t="n"/>
+      <c r="U119" s="10" t="n"/>
+      <c r="V119" s="10" t="n"/>
+      <c r="W119" s="10" t="n"/>
+      <c r="X119" s="10" t="n"/>
+      <c r="Y119" s="10" t="n"/>
+      <c r="Z119" s="10" t="n"/>
+      <c r="AA119" s="10" t="n"/>
+      <c r="AB119" s="10" t="n"/>
+      <c r="AC119" s="10" t="n"/>
+      <c r="AD119" s="10" t="n"/>
+      <c r="AE119" s="10" t="n"/>
+      <c r="AF119" s="10" t="n"/>
+      <c r="AG119" s="10" t="n"/>
+      <c r="AH119" s="10" t="n"/>
+      <c r="AI119" s="10" t="n"/>
+      <c r="AJ119" s="10" t="n"/>
+      <c r="AK119" s="11" t="n"/>
+    </row>
+    <row r="120" ht="288" customHeight="1">
+      <c r="C120" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：更新前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+{
+  "shiten_id": 1,
+  "ja_id": 1,
+  "shiten_code": "001",
+  "shiten_name": "本店営業部",
+  "shiten_name_kana": "ホンテンエイギョウブ",
+  "kinyu_shiten_flg": false,
+  "jastem_toriatsukai_tenpo_code": "001",
+  "jastem_tenpo_name": "本店",
+  "jastem_tyokin_shubetsu": "1",
+  "jastem_koza_no": "1234567",
+  "kanri_shiten_id": 1,
+  "biko": "本店ビル1F"
+}</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="n"/>
+      <c r="E120" s="10" t="n"/>
+      <c r="F120" s="10" t="n"/>
+      <c r="G120" s="10" t="n"/>
+      <c r="H120" s="10" t="n"/>
+      <c r="I120" s="10" t="n"/>
+      <c r="J120" s="10" t="n"/>
+      <c r="K120" s="10" t="n"/>
+      <c r="L120" s="10" t="n"/>
+      <c r="M120" s="10" t="n"/>
+      <c r="N120" s="10" t="n"/>
+      <c r="O120" s="10" t="n"/>
+      <c r="P120" s="10" t="n"/>
+      <c r="Q120" s="10" t="n"/>
+      <c r="R120" s="10" t="n"/>
+      <c r="S120" s="10" t="n"/>
+      <c r="T120" s="10" t="n"/>
+      <c r="U120" s="10" t="n"/>
+      <c r="V120" s="10" t="n"/>
+      <c r="W120" s="10" t="n"/>
+      <c r="X120" s="10" t="n"/>
+      <c r="Y120" s="10" t="n"/>
+      <c r="Z120" s="10" t="n"/>
+      <c r="AA120" s="10" t="n"/>
+      <c r="AB120" s="10" t="n"/>
+      <c r="AC120" s="10" t="n"/>
+      <c r="AD120" s="10" t="n"/>
+      <c r="AE120" s="10" t="n"/>
+      <c r="AF120" s="10" t="n"/>
+      <c r="AG120" s="10" t="n"/>
+      <c r="AH120" s="10" t="n"/>
+      <c r="AI120" s="10" t="n"/>
+      <c r="AJ120" s="10" t="n"/>
+      <c r="AK120" s="11" t="n"/>
+    </row>
+    <row r="121" ht="288" customHeight="1">
+      <c r="C121" s="42" t="inlineStr">
+        <is>
+          <t>`after_value`：更新後のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+{
+  "shiten_id": 1,
+  "ja_id": 1,
+  "shiten_code": "001",
+  "shiten_name": "本店営業部（名称変更）",
+  "shiten_name_kana": "ホンテンエイギョウブ",
+  "kinyu_shiten_flg": true,
+  "jastem_toriatsukai_tenpo_code": "001",
+  "jastem_tenpo_name": "本店",
+  "jastem_tyokin_shubetsu": "1",
+  "jastem_koza_no": "1234567",
+  "kanri_shiten_id": 1,
+  "biko": "本店ビル1F 改装済み"
+}</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="n"/>
+      <c r="E121" s="10" t="n"/>
+      <c r="F121" s="10" t="n"/>
+      <c r="G121" s="10" t="n"/>
+      <c r="H121" s="10" t="n"/>
+      <c r="I121" s="10" t="n"/>
+      <c r="J121" s="10" t="n"/>
+      <c r="K121" s="10" t="n"/>
+      <c r="L121" s="10" t="n"/>
+      <c r="M121" s="10" t="n"/>
+      <c r="N121" s="10" t="n"/>
+      <c r="O121" s="10" t="n"/>
+      <c r="P121" s="10" t="n"/>
+      <c r="Q121" s="10" t="n"/>
+      <c r="R121" s="10" t="n"/>
+      <c r="S121" s="10" t="n"/>
+      <c r="T121" s="10" t="n"/>
+      <c r="U121" s="10" t="n"/>
+      <c r="V121" s="10" t="n"/>
+      <c r="W121" s="10" t="n"/>
+      <c r="X121" s="10" t="n"/>
+      <c r="Y121" s="10" t="n"/>
+      <c r="Z121" s="10" t="n"/>
+      <c r="AA121" s="10" t="n"/>
+      <c r="AB121" s="10" t="n"/>
+      <c r="AC121" s="10" t="n"/>
+      <c r="AD121" s="10" t="n"/>
+      <c r="AE121" s="10" t="n"/>
+      <c r="AF121" s="10" t="n"/>
+      <c r="AG121" s="10" t="n"/>
+      <c r="AH121" s="10" t="n"/>
+      <c r="AI121" s="10" t="n"/>
+      <c r="AJ121" s="10" t="n"/>
+      <c r="AK121" s="11" t="n"/>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="B122" s="27" t="inlineStr">
+        <is>
+          <t>4.6 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="C123" s="41" t="inlineStr">
+        <is>
+          <t>更新されたデータをdata オブジェクトとして返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="B124" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="C125" s="41" t="inlineStr">
+        <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="C126" s="41" t="inlineStr">
+        <is>
+          <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="216" customHeight="1">
+      <c r="C127" s="42" t="inlineStr">
+        <is>
+          <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
+                   gamen_name, operation, result_status,
+                   target_id, target_table,
+                   before_value, after_value,
+                   error_message, stack_trace,
+                   ip_address, user_agent)
+VALUES (3, NOW(), :account_id, :ja_id,
+        '支店マスタ登録画面 (ACSMS-SCR-007)', 'UPDATE', 2,
+        :shiten_id, 'm_shiten',
+        '', '',
+        :error_message, :stack_trace,
+        :ip_address, :user_agent)</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="n"/>
+      <c r="E127" s="10" t="n"/>
+      <c r="F127" s="10" t="n"/>
+      <c r="G127" s="10" t="n"/>
+      <c r="H127" s="10" t="n"/>
+      <c r="I127" s="10" t="n"/>
+      <c r="J127" s="10" t="n"/>
+      <c r="K127" s="10" t="n"/>
+      <c r="L127" s="10" t="n"/>
+      <c r="M127" s="10" t="n"/>
+      <c r="N127" s="10" t="n"/>
+      <c r="O127" s="10" t="n"/>
+      <c r="P127" s="10" t="n"/>
+      <c r="Q127" s="10" t="n"/>
+      <c r="R127" s="10" t="n"/>
+      <c r="S127" s="10" t="n"/>
+      <c r="T127" s="10" t="n"/>
+      <c r="U127" s="10" t="n"/>
+      <c r="V127" s="10" t="n"/>
+      <c r="W127" s="10" t="n"/>
+      <c r="X127" s="10" t="n"/>
+      <c r="Y127" s="10" t="n"/>
+      <c r="Z127" s="10" t="n"/>
+      <c r="AA127" s="10" t="n"/>
+      <c r="AB127" s="10" t="n"/>
+      <c r="AC127" s="10" t="n"/>
+      <c r="AD127" s="10" t="n"/>
+      <c r="AE127" s="10" t="n"/>
+      <c r="AF127" s="10" t="n"/>
+      <c r="AG127" s="10" t="n"/>
+      <c r="AH127" s="10" t="n"/>
+      <c r="AI127" s="10" t="n"/>
+      <c r="AJ127" s="10" t="n"/>
+      <c r="AK127" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="272">
-    <mergeCell ref="B102:AK102"/>
+  <mergeCells count="282">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
@@ -12985,13 +13276,13 @@
     <mergeCell ref="AC23:AE23"/>
     <mergeCell ref="B72:I72"/>
     <mergeCell ref="D48:L48"/>
-    <mergeCell ref="A76:AK76"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M32:P32"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
+    <mergeCell ref="C86:AK86"/>
     <mergeCell ref="Y32:AB32"/>
     <mergeCell ref="C108:AK108"/>
     <mergeCell ref="J12:AK12"/>
@@ -12999,16 +13290,15 @@
     <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="D82:AK82"/>
+    <mergeCell ref="D113:AK113"/>
     <mergeCell ref="M43:P43"/>
     <mergeCell ref="Y52:AE52"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="AF50:AK50"/>
-    <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="C100:AK100"/>
+    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
@@ -13018,15 +13308,14 @@
     <mergeCell ref="D51:L51"/>
     <mergeCell ref="AF52:AK52"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="C127:AK127"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="C80:AK80"/>
-    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="J2:P3"/>
+    <mergeCell ref="B114:AK114"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
-    <mergeCell ref="C95:AK95"/>
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="M25:P25"/>
@@ -13035,15 +13324,16 @@
     <mergeCell ref="AF49:AK49"/>
     <mergeCell ref="C70:AK70"/>
     <mergeCell ref="T37:X37"/>
-    <mergeCell ref="B91:AK91"/>
     <mergeCell ref="C106:AK106"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="A21:AK21"/>
+    <mergeCell ref="B75:I75"/>
+    <mergeCell ref="D103:AK103"/>
     <mergeCell ref="T29:X29"/>
-    <mergeCell ref="B77:AK77"/>
+    <mergeCell ref="D112:AK112"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="M47:P47"/>
@@ -13059,10 +13349,11 @@
     <mergeCell ref="Q44:S44"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="AF51:AK51"/>
+    <mergeCell ref="B116:AK116"/>
+    <mergeCell ref="C126:AK126"/>
     <mergeCell ref="D89:AK89"/>
     <mergeCell ref="AC31:AE31"/>
     <mergeCell ref="AF32:AK32"/>
-    <mergeCell ref="B78:AK78"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="AF41:AK41"/>
@@ -13073,19 +13364,21 @@
     <mergeCell ref="C33:L33"/>
     <mergeCell ref="Q48:S48"/>
     <mergeCell ref="D88:AK88"/>
-    <mergeCell ref="B112:AK112"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="C103:AK103"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
+    <mergeCell ref="B78:I78"/>
     <mergeCell ref="C55:AK55"/>
     <mergeCell ref="C99:AK99"/>
+    <mergeCell ref="A82:AK82"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="T40:X40"/>
+    <mergeCell ref="C117:AK117"/>
     <mergeCell ref="C26:L26"/>
-    <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y39:AE39"/>
+    <mergeCell ref="D90:AK90"/>
     <mergeCell ref="M51:P51"/>
+    <mergeCell ref="C118:AK118"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
@@ -13107,18 +13400,22 @@
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="D52:L52"/>
     <mergeCell ref="M37:P37"/>
+    <mergeCell ref="B122:AK122"/>
     <mergeCell ref="AC33:AE33"/>
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="D49:L49"/>
+    <mergeCell ref="C125:AK125"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="Q50:S50"/>
+    <mergeCell ref="C96:AK96"/>
     <mergeCell ref="T32:X32"/>
     <mergeCell ref="B66:I66"/>
     <mergeCell ref="T45:X45"/>
+    <mergeCell ref="D102:AK102"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="Y33:AB33"/>
     <mergeCell ref="AF30:AK30"/>
@@ -13129,8 +13426,9 @@
     <mergeCell ref="C37:L37"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="D92:AK92"/>
+    <mergeCell ref="M50:P50"/>
     <mergeCell ref="C98:AK98"/>
-    <mergeCell ref="M50:P50"/>
     <mergeCell ref="C107:AK107"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
@@ -13150,14 +13448,15 @@
     <mergeCell ref="AF31:AK31"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="M49:P49"/>
+    <mergeCell ref="C121:AK121"/>
     <mergeCell ref="M39:P39"/>
+    <mergeCell ref="B84:AK84"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="B69:I69"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="Y30:AB30"/>
-    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="C105:AK105"/>
@@ -13168,11 +13467,12 @@
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="D96:AK96"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="AC32:AE32"/>
+    <mergeCell ref="C120:AK120"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="T43:X43"/>
+    <mergeCell ref="C119:AK119"/>
     <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="D46:L46"/>
     <mergeCell ref="T52:X52"/>
@@ -13185,6 +13485,7 @@
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="C67:AK67"/>
     <mergeCell ref="Y46:AE46"/>
+    <mergeCell ref="D91:AK91"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
@@ -13198,43 +13499,44 @@
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="Y48:AE48"/>
+    <mergeCell ref="D93:AK93"/>
     <mergeCell ref="AC26:AE26"/>
-    <mergeCell ref="C92:AK92"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="A35:AK35"/>
     <mergeCell ref="D43:L43"/>
-    <mergeCell ref="D83:AK83"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="Y47:AE47"/>
     <mergeCell ref="B60:I60"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="D85:AK85"/>
     <mergeCell ref="B57:I57"/>
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="M52:P52"/>
+    <mergeCell ref="D100:AK100"/>
     <mergeCell ref="AC27:AE27"/>
+    <mergeCell ref="B83:AK83"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="D50:L50"/>
-    <mergeCell ref="D84:AK84"/>
     <mergeCell ref="D44:L44"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="Y51:AE51"/>
+    <mergeCell ref="B124:AK124"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="C90:AK90"/>
     <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="B110:AK110"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="D86:AK86"/>
+    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="Y50:AE50"/>
+    <mergeCell ref="D95:AK95"/>
     <mergeCell ref="AC28:AE28"/>
+    <mergeCell ref="C76:AK76"/>
     <mergeCell ref="M30:P30"/>
+    <mergeCell ref="C110:AK110"/>
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="D45:L45"/>
